--- a/projectlog.xlsx
+++ b/projectlog.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jesus\Documents\epq\epqamogus\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{301AE075-50A4-4DA5-9DB9-75B138EE1949}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A5D2CE4-E8B1-4790-9900-C17D16B9E011}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{EDB5D72F-48E2-4CB8-9502-BD53B6BDCEDE}"/>
   </bookViews>
@@ -33,6 +33,116 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="35">
+  <si>
+    <t>week start</t>
+  </si>
+  <si>
+    <t>month</t>
+  </si>
+  <si>
+    <t>comments</t>
+  </si>
+  <si>
+    <t>introductory session</t>
+  </si>
+  <si>
+    <t>Discussed different areas such as history during Victorian era and game projects with teachers.  Submitted internal application</t>
+  </si>
+  <si>
+    <t>followed up and decided on a project that would intergrate LLMs into playing a game.</t>
+  </si>
+  <si>
+    <t>first taught session</t>
+  </si>
+  <si>
+    <t>second taught session, drafted application form</t>
+  </si>
+  <si>
+    <t>Discussed scope with supervisor, adjusted and submitted application form. Deciding on ambition of project</t>
+  </si>
+  <si>
+    <t>Had an EPQ taught session about researching papers and the best practices on taking notes. Not as applicable compared to a disseration, but still helpful nonetheless</t>
+  </si>
+  <si>
+    <t>looked into finding an API or something similar to try and interact with the game/ read gamestates</t>
+  </si>
+  <si>
+    <t>i had come across a couple deprecated apis and ones that simply just didn’t work and many stated that they had not been updated</t>
+  </si>
+  <si>
+    <t>christmas</t>
+  </si>
+  <si>
+    <t>decided against using apis or similar due to lack of avalibility, and instead pivoted towards using image capture</t>
+  </si>
+  <si>
+    <t>resubmitted form with amendments</t>
+  </si>
+  <si>
+    <t>Had an EPQ taught session about using resources</t>
+  </si>
+  <si>
+    <t>looked at many different LLMs, decided on one with a range about ~8B parameters, lots of testing and prompting, lots of them would keep generating extremely long text with many sentences despite me telling it not to, however some newer models such as mistral and meta ones would give me actual one sentence returns. thought about using json format in order to just get the text and not useless information, but decided against it as many models do not have this functionality</t>
+  </si>
+  <si>
+    <t>decided on "Hermes-3-Llama-3.1-8B-GGUF:Q8_0", a finetuned version of llama3 from meta, and created prompts for voting and chatting</t>
+  </si>
+  <si>
+    <t>worked on using pyscreeze to capture images to cross reference across the screen to see if certain components were there or not</t>
+  </si>
+  <si>
+    <t>taught session on arguments and counter arguments. Will remember for the 'deciding on what to use' parts</t>
+  </si>
+  <si>
+    <t>ran into some issues where the images using pyscreeze were not recognised by pyautogui. I thought this was strange as if its just capturing pixels then whats the difference</t>
+  </si>
+  <si>
+    <t>fixed aforementioned issue by instead using pyautogui to take the screenshots in specific regions, using a python script I developed where pressing certain keys would give pixel information such as location etc. I saved these to a folder for use</t>
+  </si>
+  <si>
+    <t>epq taught session for ONLY artefacts (there was three of us), very useful, flexibility and the journey was emphasised</t>
+  </si>
+  <si>
+    <t>worked on being able to use those images to read the game state, using the report button for knowing chat is open, the map icon for being able to walk around, and a little icon for the lobby</t>
+  </si>
+  <si>
+    <t>continued working on reading game state, eventually deciding on using the 'signal bar' icon in the corner of the tablet in meeting to recognise meetings since that is a static image that does not get different colors/shaded compared to some others. Lots of testing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">began work on making the bot chat, and reading text of the screen in the chat menu (only during voting). Ran into an issue where it would try to chat while dead because it had the chat icon up, so changed it so the chat icon was up and the map was NOT. to read chat i would take a screenshot of the chat region, store it was temp.png, and read all the text from there which would be put into messages (the array) formatted as a dictionary so it can be fed into the llm. </t>
+  </si>
+  <si>
+    <t>had to fix some of the prompts as some of the chat text was nonsensical and it would get confused 'please give me more context' NO SHUSH. also to make it more aware of whats happening, i would give it the messages it had said previously so it didnt contradict itself (resets every round). this seems to have fixed most of the issues where it would not adhere to the prompt of being human and would instead ask for more context</t>
+  </si>
+  <si>
+    <t>worked on voting, by using the prompt (which had to be modified slightly) to select someone to vote. However to find them is only slightly functional, as I use srceenshots of each color (thanks colorblind mode), and so if people have bright and colorful banners it wont work as well. failing to find the person will just mean random votes. implemented skipping voting as well, which was tough as the confirm button is in a different place to the original button press, unlike the others where you can just double click, so i circumvented this by having the mouse go back to where the confirm button WOULD be if you pressed skip everytime and click it.</t>
+  </si>
+  <si>
+    <t>added movement in lobby and in game to seem more human. Originally I made it so that it would choose a random number 1-4, and it would go into a direction corresponding to that number for a random amount of time (a random number between 0-1 * a random number between 0-1). this seemed to work well in the waiting lobby, however in the real game it would often get stuck walking in one direction for too long and would hit a wall or obstacle and so would just stay there. to prevent this i made it move much more frequently, and instead of moving in a direction for a certain amount of time it would 'press' or 'release' keys, by choosing 1-8 where 1-4 is pressing the key and 5-8 is releasing it. this also caused issues where it would hold opposite keys and go nowhere since they cancel out. so instead i switched back to 1-4, but it would release the opposite key and press the direction key, so this was no longer a problem and it would move more. i also removed the time so it just happens every update.</t>
+  </si>
+  <si>
+    <t>made it able to continue into more games, through pressing the buttons required to continue back to the lobby (e.g once I leave it in a lobby it can just keep going). Just let it run for a while, up to 13k beans</t>
+  </si>
+  <si>
+    <t>epq taught session on drafting an epq, a lot of it was not as useful for a artefact and the sheets were for not given to us artefactors</t>
+  </si>
+  <si>
+    <t>made the chat reading better by eliminating all non black pixels and replacing it with white. This way background text such as playernames is no longer considered when reading (used https://stackoverflow.com/questions/60817066/i-want-to-replace-all-of-the-things-which-are-not-black-text-and-white-backgroun)</t>
+  </si>
+  <si>
+    <t>unable to do much due to exams</t>
+  </si>
+  <si>
+    <t>fixed small problems where the log would be all one line, and the winlose ratio not properly recorded and calculated as it would put it on a newline which meant it effectively wasn’t recording anything</t>
+  </si>
+  <si>
+    <t>added lots of comments to the code explaining the purpose of each snippet</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -402,9 +512,517 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B92A4109-9015-47BA-9FCF-069B0316B3D9}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:C50"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="9.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="255.6328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>23</v>
+      </c>
+      <c r="B2">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>30</v>
+      </c>
+      <c r="B3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>7</v>
+      </c>
+      <c r="B4">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>14</v>
+      </c>
+      <c r="B5">
+        <v>10</v>
+      </c>
+      <c r="C5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>21</v>
+      </c>
+      <c r="B6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>28</v>
+      </c>
+      <c r="B7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>4</v>
+      </c>
+      <c r="B8">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>11</v>
+      </c>
+      <c r="B9">
+        <v>11</v>
+      </c>
+      <c r="C9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>18</v>
+      </c>
+      <c r="B10">
+        <v>11</v>
+      </c>
+      <c r="C10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>25</v>
+      </c>
+      <c r="B11">
+        <v>11</v>
+      </c>
+      <c r="C11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>2</v>
+      </c>
+      <c r="B12">
+        <v>12</v>
+      </c>
+      <c r="C12" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>9</v>
+      </c>
+      <c r="B13">
+        <v>12</v>
+      </c>
+      <c r="C13" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>16</v>
+      </c>
+      <c r="B14">
+        <v>12</v>
+      </c>
+      <c r="C14" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>23</v>
+      </c>
+      <c r="B15">
+        <v>12</v>
+      </c>
+      <c r="C15" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>30</v>
+      </c>
+      <c r="B16">
+        <v>12</v>
+      </c>
+      <c r="C16" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>6</v>
+      </c>
+      <c r="B17">
+        <v>1</v>
+      </c>
+      <c r="C17" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>13</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>20</v>
+      </c>
+      <c r="B19">
+        <v>1</v>
+      </c>
+      <c r="C19" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>27</v>
+      </c>
+      <c r="B20">
+        <v>1</v>
+      </c>
+      <c r="C20" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>3</v>
+      </c>
+      <c r="B21">
+        <v>2</v>
+      </c>
+      <c r="C21" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>10</v>
+      </c>
+      <c r="B22">
+        <v>2</v>
+      </c>
+      <c r="C22" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>17</v>
+      </c>
+      <c r="B23">
+        <v>2</v>
+      </c>
+      <c r="C23" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A24">
+        <v>24</v>
+      </c>
+      <c r="B24">
+        <v>2</v>
+      </c>
+      <c r="C24" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A25">
+        <v>3</v>
+      </c>
+      <c r="B25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A26">
+        <v>10</v>
+      </c>
+      <c r="B26">
+        <v>3</v>
+      </c>
+      <c r="C26" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A27">
+        <v>17</v>
+      </c>
+      <c r="B27">
+        <v>3</v>
+      </c>
+      <c r="C27" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A28">
+        <v>24</v>
+      </c>
+      <c r="B28">
+        <v>3</v>
+      </c>
+      <c r="C28" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A29">
+        <v>31</v>
+      </c>
+      <c r="B29">
+        <v>3</v>
+      </c>
+      <c r="C29" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A30">
+        <v>7</v>
+      </c>
+      <c r="B30">
+        <v>4</v>
+      </c>
+      <c r="C30" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A31">
+        <v>14</v>
+      </c>
+      <c r="B31">
+        <v>4</v>
+      </c>
+      <c r="C31" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A32">
+        <v>21</v>
+      </c>
+      <c r="B32">
+        <v>4</v>
+      </c>
+      <c r="C32" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A33">
+        <v>28</v>
+      </c>
+      <c r="B33">
+        <v>4</v>
+      </c>
+      <c r="C33" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A34">
+        <v>5</v>
+      </c>
+      <c r="B34">
+        <v>5</v>
+      </c>
+      <c r="C34" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A35">
+        <v>12</v>
+      </c>
+      <c r="B35">
+        <v>5</v>
+      </c>
+      <c r="C35" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A36">
+        <v>19</v>
+      </c>
+      <c r="B36">
+        <v>5</v>
+      </c>
+      <c r="C36" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A37">
+        <v>26</v>
+      </c>
+      <c r="B37">
+        <v>5</v>
+      </c>
+      <c r="C37" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A38">
+        <v>2</v>
+      </c>
+      <c r="B38">
+        <v>6</v>
+      </c>
+      <c r="C38" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A39">
+        <v>9</v>
+      </c>
+      <c r="B39">
+        <v>6</v>
+      </c>
+      <c r="C39" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A40">
+        <v>16</v>
+      </c>
+      <c r="B40">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A41">
+        <v>23</v>
+      </c>
+      <c r="B41">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A42">
+        <v>30</v>
+      </c>
+      <c r="B42">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A43">
+        <v>7</v>
+      </c>
+      <c r="B43">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A44">
+        <v>14</v>
+      </c>
+      <c r="B44">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A45">
+        <v>21</v>
+      </c>
+      <c r="B45">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A46">
+        <v>28</v>
+      </c>
+      <c r="B46">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A47">
+        <v>4</v>
+      </c>
+      <c r="B47">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A48">
+        <v>11</v>
+      </c>
+      <c r="B48">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A49">
+        <v>18</v>
+      </c>
+      <c r="B49">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A50">
+        <v>25</v>
+      </c>
+      <c r="B50">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/projectlog.xlsx
+++ b/projectlog.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jesus\Documents\epq\epqamogus\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A5D2CE4-E8B1-4790-9900-C17D16B9E011}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{552C7485-F1E2-420B-9B89-A7E6BAD9DDCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{EDB5D72F-48E2-4CB8-9502-BD53B6BDCEDE}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="50">
   <si>
     <t>week start</t>
   </si>
@@ -116,9 +116,6 @@
     <t xml:space="preserve">began work on making the bot chat, and reading text of the screen in the chat menu (only during voting). Ran into an issue where it would try to chat while dead because it had the chat icon up, so changed it so the chat icon was up and the map was NOT. to read chat i would take a screenshot of the chat region, store it was temp.png, and read all the text from there which would be put into messages (the array) formatted as a dictionary so it can be fed into the llm. </t>
   </si>
   <si>
-    <t>had to fix some of the prompts as some of the chat text was nonsensical and it would get confused 'please give me more context' NO SHUSH. also to make it more aware of whats happening, i would give it the messages it had said previously so it didnt contradict itself (resets every round). this seems to have fixed most of the issues where it would not adhere to the prompt of being human and would instead ask for more context</t>
-  </si>
-  <si>
     <t>worked on voting, by using the prompt (which had to be modified slightly) to select someone to vote. However to find them is only slightly functional, as I use srceenshots of each color (thanks colorblind mode), and so if people have bright and colorful banners it wont work as well. failing to find the person will just mean random votes. implemented skipping voting as well, which was tough as the confirm button is in a different place to the original button press, unlike the others where you can just double click, so i circumvented this by having the mouse go back to where the confirm button WOULD be if you pressed skip everytime and click it.</t>
   </si>
   <si>
@@ -134,13 +131,61 @@
     <t>made the chat reading better by eliminating all non black pixels and replacing it with white. This way background text such as playernames is no longer considered when reading (used https://stackoverflow.com/questions/60817066/i-want-to-replace-all-of-the-things-which-are-not-black-text-and-white-backgroun)</t>
   </si>
   <si>
-    <t>unable to do much due to exams</t>
-  </si>
-  <si>
     <t>fixed small problems where the log would be all one line, and the winlose ratio not properly recorded and calculated as it would put it on a newline which meant it effectively wasn’t recording anything</t>
   </si>
   <si>
     <t>added lots of comments to the code explaining the purpose of each snippet</t>
+  </si>
+  <si>
+    <t>had an EPQ taught session, which highlighted the importance of evaluation section, and information about the presentations. This helped me plan my presentation, to be a lot less dependent on 'visual aids'</t>
+  </si>
+  <si>
+    <t>had a meeting with my EPQ supervisor to look at feedback of my first draft, including to better explain some of the concepts and have a more understandable progression, and later had a meeting with Dr Williams to better discuss the structure and phrasing of my project report, and the use of images/videos</t>
+  </si>
+  <si>
+    <t>I spent this week planning and creating the slides for my presentation, and ensuring its around 8 minutes. I mainly focused on the evaluation and afterthoughts, with only a brief explanation of the inner workings of the project</t>
+  </si>
+  <si>
+    <t>had to fix some of the prompts as some of the chat text was nonsensical and it would get confused 'please give me more context'. also to make it more aware of whats happening, i would give it the messages it had said previously so it didnt contradict itself (resets every round). this seems to have fixed most of the issues where it would not adhere to the prompt of being human and would instead ask for more context</t>
+  </si>
+  <si>
+    <t>I now wanted to expand the bot's abilities to include the ability to do tasks. I started adding tasks, added inspect sample, clear asteroids, and calibrate distributor.</t>
+  </si>
+  <si>
+    <t>I added more tasks, adding align engine input which was a little more difficult as it had a curved interface, meaning I had to think about it more. I also added fix wiring, which was complicated as well due to the colours being random but was the most common task.</t>
+  </si>
+  <si>
+    <t>this week I added the simon says task, called start reactor. This was hard as even as a human I couldn’t finish it all of the time. But through lots of colour recognition, I managed to do it. I also added the card swipe, which was harder than anticipated but only because of some technical difficulties of registering the movement of the mouse.</t>
+  </si>
+  <si>
+    <t>I added some of the more simple tasks, like empty chute, stabilise steering, and divert power which mostly consisted of clicking specific things on the screen which it recognises. These were a lot simpler than the other ones</t>
+  </si>
+  <si>
+    <t>I added more tasks of upload data (which was another click a single button task), clean vent (lots of random clicking), and prime shields which had clicking in pre-determined areas. These were all a lot easier.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I didn't do much this week, just some minor tweaks to the prompt, removing a lot of fluff and replacing it with more concise instructions. </t>
+  </si>
+  <si>
+    <t>I did my presentation, which I think went well. I skipped a few bits I wanted to touch on due to time, and also didn’t realise there was some audio in some of my videos.</t>
+  </si>
+  <si>
+    <t>I spent this week practicing for TMUA as it was on the 14th.</t>
+  </si>
+  <si>
+    <t>I modified the draft according to supervisor feedback</t>
+  </si>
+  <si>
+    <t>I had to change the format of the log from excel spreadsheet into the word document, and gather all the stuff needed for submission, and finally submit it.</t>
+  </si>
+  <si>
+    <t>unable to do much due to end of year exams</t>
+  </si>
+  <si>
+    <t>I improved a lot of the menu navigation, allowing it to play lots of games with no interuption, to the point where I could leave it overnight and it would still be running in the morning.</t>
+  </si>
+  <si>
+    <t>I didn’t do much this week, mostly just run it and collect data.</t>
   </si>
 </sst>
 </file>
@@ -512,7 +557,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B92A4109-9015-47BA-9FCF-069B0316B3D9}">
-  <dimension ref="A1:C50"/>
+  <dimension ref="A1:C59"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.1796875" bestFit="1" customWidth="1"/>
@@ -832,7 +877,7 @@
         <v>4</v>
       </c>
       <c r="C30" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
@@ -843,7 +888,7 @@
         <v>4</v>
       </c>
       <c r="C31" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.35">
@@ -854,7 +899,7 @@
         <v>4</v>
       </c>
       <c r="C32" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.35">
@@ -865,7 +910,7 @@
         <v>4</v>
       </c>
       <c r="C33" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.35">
@@ -876,7 +921,7 @@
         <v>5</v>
       </c>
       <c r="C34" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.35">
@@ -887,7 +932,7 @@
         <v>5</v>
       </c>
       <c r="C35" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.35">
@@ -898,7 +943,7 @@
         <v>5</v>
       </c>
       <c r="C36" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.35">
@@ -909,7 +954,7 @@
         <v>5</v>
       </c>
       <c r="C37" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.35">
@@ -920,7 +965,7 @@
         <v>6</v>
       </c>
       <c r="C38" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.35">
@@ -931,7 +976,7 @@
         <v>6</v>
       </c>
       <c r="C39" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.35">
@@ -941,6 +986,9 @@
       <c r="B40">
         <v>6</v>
       </c>
+      <c r="C40" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41">
@@ -949,6 +997,9 @@
       <c r="B41">
         <v>6</v>
       </c>
+      <c r="C41" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42">
@@ -965,6 +1016,9 @@
       <c r="B43">
         <v>7</v>
       </c>
+      <c r="C43" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44">
@@ -973,6 +1027,9 @@
       <c r="B44">
         <v>7</v>
       </c>
+      <c r="C44" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45">
@@ -981,6 +1038,9 @@
       <c r="B45">
         <v>7</v>
       </c>
+      <c r="C45" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46">
@@ -989,6 +1049,9 @@
       <c r="B46">
         <v>7</v>
       </c>
+      <c r="C46" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47">
@@ -997,6 +1060,9 @@
       <c r="B47">
         <v>8</v>
       </c>
+      <c r="C47" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48">
@@ -1005,8 +1071,11 @@
       <c r="B48">
         <v>8</v>
       </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C48" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>18</v>
       </c>
@@ -1014,12 +1083,108 @@
         <v>8</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>25</v>
       </c>
       <c r="B50">
         <v>8</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A51">
+        <v>1</v>
+      </c>
+      <c r="B51">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A52">
+        <v>8</v>
+      </c>
+      <c r="B52">
+        <v>9</v>
+      </c>
+      <c r="C52" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A53">
+        <v>15</v>
+      </c>
+      <c r="B53">
+        <v>9</v>
+      </c>
+      <c r="C53" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A54">
+        <v>22</v>
+      </c>
+      <c r="B54">
+        <v>9</v>
+      </c>
+      <c r="C54" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A55">
+        <v>29</v>
+      </c>
+      <c r="B55">
+        <v>9</v>
+      </c>
+      <c r="C55" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A56">
+        <v>6</v>
+      </c>
+      <c r="B56">
+        <v>10</v>
+      </c>
+      <c r="C56" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A57">
+        <v>13</v>
+      </c>
+      <c r="B57">
+        <v>10</v>
+      </c>
+      <c r="C57" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A58">
+        <v>20</v>
+      </c>
+      <c r="B58">
+        <v>10</v>
+      </c>
+      <c r="C58" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A59">
+        <v>27</v>
+      </c>
+      <c r="B59">
+        <v>10</v>
+      </c>
+      <c r="C59" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>
